--- a/outputs/tables/result2.xlsx
+++ b/outputs/tables/result2.xlsx
@@ -7396,10 +7396,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>2.087670</v>
+        <v>1.209931</v>
       </c>
       <c r="C2">
-        <v>-0.610477</v>
+        <v>1.942784</v>
       </c>
       <c r="D2">
         <v>1.000000</v>
@@ -7412,13 +7412,13 @@
         </is>
       </c>
       <c r="B3">
-        <v>1.036454</v>
+        <v>-1.643792</v>
       </c>
       <c r="C3">
-        <v>2.049325</v>
+        <v>1.753399</v>
       </c>
       <c r="D3">
-        <v>0.989215</v>
+        <v>0.991551</v>
       </c>
     </row>
     <row r="4">
@@ -7428,13 +7428,13 @@
         </is>
       </c>
       <c r="B4">
-        <v>-0.596894</v>
+        <v>-2.444283</v>
       </c>
       <c r="C4">
-        <v>2.283149</v>
+        <v>0.310584</v>
       </c>
       <c r="D4">
-        <v>0.987969</v>
+        <v>0.990516</v>
       </c>
     </row>
     <row r="5">
@@ -7444,13 +7444,13 @@
         </is>
       </c>
       <c r="B5">
-        <v>-1.983584</v>
+        <v>-2.153948</v>
       </c>
       <c r="C5">
-        <v>1.388951</v>
+        <v>-1.313671</v>
       </c>
       <c r="D5">
-        <v>0.986857</v>
+        <v>0.989583</v>
       </c>
     </row>
     <row r="6">
@@ -7460,13 +7460,13 @@
         </is>
       </c>
       <c r="B6">
-        <v>-2.474575</v>
+        <v>-0.921273</v>
       </c>
       <c r="C6">
-        <v>-0.186304</v>
+        <v>-2.410490</v>
       </c>
       <c r="D6">
-        <v>0.985859</v>
+        <v>0.988738</v>
       </c>
     </row>
     <row r="7">
@@ -7476,13 +7476,13 @@
         </is>
       </c>
       <c r="B7">
-        <v>-1.868380</v>
+        <v>0.723984</v>
       </c>
       <c r="C7">
-        <v>-1.720914</v>
+        <v>-2.535510</v>
       </c>
       <c r="D7">
-        <v>0.984957</v>
+        <v>0.987968</v>
       </c>
     </row>
     <row r="8">
@@ -7492,13 +7492,13 @@
         </is>
       </c>
       <c r="B8">
-        <v>-0.446860</v>
+        <v>2.121047</v>
       </c>
       <c r="C8">
-        <v>-2.558636</v>
+        <v>-1.657607</v>
       </c>
       <c r="D8">
-        <v>0.984139</v>
+        <v>0.987264</v>
       </c>
     </row>
     <row r="9">
@@ -7508,13 +7508,13 @@
         </is>
       </c>
       <c r="B9">
-        <v>1.192355</v>
+        <v>2.742835</v>
       </c>
       <c r="C9">
-        <v>-2.370291</v>
+        <v>-0.129248</v>
       </c>
       <c r="D9">
-        <v>0.983393</v>
+        <v>0.986618</v>
       </c>
     </row>
     <row r="10">
@@ -7524,13 +7524,13 @@
         </is>
       </c>
       <c r="B10">
-        <v>2.402808</v>
+        <v>2.375787</v>
       </c>
       <c r="C10">
-        <v>-1.248995</v>
+        <v>1.479409</v>
       </c>
       <c r="D10">
-        <v>0.982710</v>
+        <v>0.986023</v>
       </c>
     </row>
     <row r="11">
@@ -7540,13 +7540,13 @@
         </is>
       </c>
       <c r="B11">
-        <v>2.737197</v>
+        <v>1.165882</v>
       </c>
       <c r="C11">
-        <v>0.366766</v>
+        <v>2.601295</v>
       </c>
       <c r="D11">
-        <v>0.982082</v>
+        <v>0.985472</v>
       </c>
     </row>
     <row r="12">
@@ -7556,13 +7556,13 @@
         </is>
       </c>
       <c r="B12">
-        <v>2.090050</v>
+        <v>-0.463014</v>
       </c>
       <c r="C12">
-        <v>1.884561</v>
+        <v>2.864347</v>
       </c>
       <c r="D12">
-        <v>0.981503</v>
+        <v>0.984962</v>
       </c>
     </row>
     <row r="13">
@@ -7572,13 +7572,13 @@
         </is>
       </c>
       <c r="B13">
-        <v>0.703023</v>
+        <v>-1.971737</v>
       </c>
       <c r="C13">
-        <v>2.778236</v>
+        <v>2.196322</v>
       </c>
       <c r="D13">
-        <v>0.980968</v>
+        <v>0.984487</v>
       </c>
     </row>
     <row r="14">
@@ -7588,13 +7588,13 @@
         </is>
       </c>
       <c r="B14">
-        <v>-0.946858</v>
+        <v>-2.885737</v>
       </c>
       <c r="C14">
-        <v>2.758460</v>
+        <v>0.822603</v>
       </c>
       <c r="D14">
-        <v>0.980470</v>
+        <v>0.984045</v>
       </c>
     </row>
     <row r="15">
@@ -7604,13 +7604,13 @@
         </is>
       </c>
       <c r="B15">
-        <v>-2.321676</v>
+        <v>-2.934830</v>
       </c>
       <c r="C15">
-        <v>1.846113</v>
+        <v>-0.826666</v>
       </c>
       <c r="D15">
-        <v>0.980008</v>
+        <v>0.983632</v>
       </c>
     </row>
     <row r="16">
@@ -7620,13 +7620,13 @@
         </is>
       </c>
       <c r="B16">
-        <v>-2.995858</v>
+        <v>-2.117133</v>
       </c>
       <c r="C16">
-        <v>0.340132</v>
+        <v>-2.259799</v>
       </c>
       <c r="D16">
-        <v>0.979577</v>
+        <v>0.983245</v>
       </c>
     </row>
     <row r="17">
@@ -7636,13 +7636,13 @@
         </is>
       </c>
       <c r="B17">
-        <v>-2.775944</v>
+        <v>-0.679277</v>
       </c>
       <c r="C17">
-        <v>-1.295147</v>
+        <v>-3.069163</v>
       </c>
       <c r="D17">
-        <v>0.979173</v>
+        <v>0.982882</v>
       </c>
     </row>
     <row r="18">
@@ -7652,13 +7652,13 @@
         </is>
       </c>
       <c r="B18">
-        <v>-1.739300</v>
+        <v>0.970436</v>
       </c>
       <c r="C18">
-        <v>-2.578840</v>
+        <v>-3.038348</v>
       </c>
       <c r="D18">
-        <v>0.978795</v>
+        <v>0.982540</v>
       </c>
     </row>
     <row r="19">
@@ -7668,13 +7668,13 @@
         </is>
       </c>
       <c r="B19">
-        <v>-0.191806</v>
+        <v>2.383812</v>
       </c>
       <c r="C19">
-        <v>-3.151347</v>
+        <v>-2.186957</v>
       </c>
       <c r="D19">
-        <v>0.978440</v>
+        <v>0.982218</v>
       </c>
     </row>
     <row r="20">
@@ -7684,13 +7684,13 @@
         </is>
       </c>
       <c r="B20">
-        <v>1.433092</v>
+        <v>3.193143</v>
       </c>
       <c r="C20">
-        <v>-2.864633</v>
+        <v>-0.749082</v>
       </c>
       <c r="D20">
-        <v>0.978106</v>
+        <v>0.981915</v>
       </c>
     </row>
     <row r="21">
@@ -7700,13 +7700,13 @@
         </is>
       </c>
       <c r="B21">
-        <v>2.699453</v>
+        <v>3.199611</v>
       </c>
       <c r="C21">
-        <v>-1.806886</v>
+        <v>0.900905</v>
       </c>
       <c r="D21">
-        <v>0.977791</v>
+        <v>0.981628</v>
       </c>
     </row>
     <row r="22">
@@ -7716,13 +7716,13 @@
         </is>
       </c>
       <c r="B22">
-        <v>3.282449</v>
+        <v>2.411588</v>
       </c>
       <c r="C22">
-        <v>-0.263313</v>
+        <v>2.350567</v>
       </c>
       <c r="D22">
-        <v>0.977494</v>
+        <v>0.981356</v>
       </c>
     </row>
     <row r="23">
@@ -7732,13 +7732,13 @@
         </is>
       </c>
       <c r="B23">
-        <v>3.043158</v>
+        <v>1.029346</v>
       </c>
       <c r="C23">
-        <v>1.369243</v>
+        <v>3.251626</v>
       </c>
       <c r="D23">
-        <v>0.977213</v>
+        <v>0.981098</v>
       </c>
     </row>
     <row r="24">
@@ -7748,13 +7748,13 @@
         </is>
       </c>
       <c r="B24">
-        <v>2.050691</v>
+        <v>-0.614140</v>
       </c>
       <c r="C24">
-        <v>2.687389</v>
+        <v>3.398100</v>
       </c>
       <c r="D24">
-        <v>0.976947</v>
+        <v>0.980854</v>
       </c>
     </row>
     <row r="25">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="B25">
-        <v>0.552382</v>
+        <v>-2.137859</v>
       </c>
       <c r="C25">
-        <v>3.378454</v>
+        <v>2.765027</v>
       </c>
       <c r="D25">
-        <v>0.976694</v>
+        <v>0.980621</v>
       </c>
     </row>
     <row r="26">
@@ -7780,13 +7780,13 @@
         </is>
       </c>
       <c r="B26">
-        <v>-1.095140</v>
+        <v>-3.201149</v>
       </c>
       <c r="C26">
-        <v>3.288062</v>
+        <v>1.503316</v>
       </c>
       <c r="D26">
-        <v>0.976454</v>
+        <v>0.980399</v>
       </c>
     </row>
     <row r="27">
@@ -7796,13 +7796,13 @@
         </is>
       </c>
       <c r="B27">
-        <v>-2.513992</v>
+        <v>-3.576035</v>
       </c>
       <c r="C27">
-        <v>2.445827</v>
+        <v>-0.103531</v>
       </c>
       <c r="D27">
-        <v>0.976226</v>
+        <v>0.980188</v>
       </c>
     </row>
     <row r="28">
@@ -7812,13 +7812,13 @@
         </is>
       </c>
       <c r="B28">
-        <v>-3.390518</v>
+        <v>-3.189674</v>
       </c>
       <c r="C28">
-        <v>1.047899</v>
+        <v>-1.707659</v>
       </c>
       <c r="D28">
-        <v>0.976008</v>
+        <v>0.979987</v>
       </c>
     </row>
     <row r="29">
@@ -7828,13 +7828,13 @@
         </is>
       </c>
       <c r="B29">
-        <v>-3.539874</v>
+        <v>-2.131010</v>
       </c>
       <c r="C29">
-        <v>-0.595327</v>
+        <v>-2.973254</v>
       </c>
       <c r="D29">
-        <v>0.975801</v>
+        <v>0.979795</v>
       </c>
     </row>
     <row r="30">
@@ -7844,13 +7844,13 @@
         </is>
       </c>
       <c r="B30">
-        <v>-2.938100</v>
+        <v>-0.623792</v>
       </c>
       <c r="C30">
-        <v>-2.131676</v>
+        <v>-3.644666</v>
       </c>
       <c r="D30">
-        <v>0.975603</v>
+        <v>0.979611</v>
       </c>
     </row>
     <row r="31">
@@ -7860,13 +7860,13 @@
         </is>
       </c>
       <c r="B31">
-        <v>-1.718253</v>
+        <v>1.025411</v>
       </c>
       <c r="C31">
-        <v>-3.242744</v>
+        <v>-3.593390</v>
       </c>
       <c r="D31">
-        <v>0.975414</v>
+        <v>0.979435</v>
       </c>
     </row>
     <row r="32">
@@ -7876,13 +7876,13 @@
         </is>
       </c>
       <c r="B32">
-        <v>-0.134872</v>
+        <v>2.491658</v>
       </c>
       <c r="C32">
-        <v>-3.706864</v>
+        <v>-2.836674</v>
       </c>
       <c r="D32">
-        <v>0.975234</v>
+        <v>0.979266</v>
       </c>
     </row>
     <row r="33">
@@ -7892,13 +7892,13 @@
         </is>
       </c>
       <c r="B33">
-        <v>1.493100</v>
+        <v>3.495010</v>
       </c>
       <c r="C33">
-        <v>-3.438151</v>
+        <v>-1.526794</v>
       </c>
       <c r="D33">
-        <v>0.975061</v>
+        <v>0.979104</v>
       </c>
     </row>
     <row r="34">
@@ -7908,13 +7908,13 @@
         </is>
       </c>
       <c r="B34">
-        <v>2.847834</v>
+        <v>3.850993</v>
       </c>
       <c r="C34">
-        <v>-2.496240</v>
+        <v>0.084348</v>
       </c>
       <c r="D34">
-        <v>0.974895</v>
+        <v>0.978949</v>
       </c>
     </row>
     <row r="35">
@@ -7924,13 +7924,13 @@
         </is>
       </c>
       <c r="B35">
-        <v>3.673258</v>
+        <v>3.499987</v>
       </c>
       <c r="C35">
-        <v>-1.067544</v>
+        <v>1.696580</v>
       </c>
       <c r="D35">
-        <v>0.974736</v>
+        <v>0.978800</v>
       </c>
     </row>
     <row r="36">
@@ -7940,13 +7940,13 @@
         </is>
       </c>
       <c r="B36">
-        <v>3.819927</v>
+        <v>2.512029</v>
       </c>
       <c r="C36">
-        <v>0.575925</v>
+        <v>3.018110</v>
       </c>
       <c r="D36">
-        <v>0.974583</v>
+        <v>0.978657</v>
       </c>
     </row>
     <row r="37">
@@ -7956,13 +7956,13 @@
         </is>
       </c>
       <c r="B37">
-        <v>3.267265</v>
+        <v>1.068290</v>
       </c>
       <c r="C37">
-        <v>2.130616</v>
+        <v>3.816933</v>
       </c>
       <c r="D37">
-        <v>0.974436</v>
+        <v>0.978519</v>
       </c>
     </row>
     <row r="38">
@@ -7972,13 +7972,13 @@
         </is>
       </c>
       <c r="B38">
-        <v>2.121131</v>
+        <v>-0.575625</v>
       </c>
       <c r="C38">
-        <v>3.317577</v>
+        <v>3.958507</v>
       </c>
       <c r="D38">
-        <v>0.974295</v>
+        <v>0.978386</v>
       </c>
     </row>
     <row r="39">
@@ -7988,13 +7988,13 @@
         </is>
       </c>
       <c r="B39">
-        <v>0.589219</v>
+        <v>-2.136772</v>
       </c>
       <c r="C39">
-        <v>3.930556</v>
+        <v>3.424353</v>
       </c>
       <c r="D39">
-        <v>0.974160</v>
+        <v>0.978258</v>
       </c>
     </row>
     <row r="40">
@@ -8004,13 +8004,13 @@
         </is>
       </c>
       <c r="B40">
-        <v>-1.059611</v>
+        <v>-3.353616</v>
       </c>
       <c r="C40">
-        <v>3.868407</v>
+        <v>2.309996</v>
       </c>
       <c r="D40">
-        <v>0.974029</v>
+        <v>0.978135</v>
       </c>
     </row>
     <row r="41">
@@ -8020,13 +8020,13 @@
         </is>
       </c>
       <c r="B41">
-        <v>-2.543823</v>
+        <v>-4.028256</v>
       </c>
       <c r="C41">
-        <v>3.147565</v>
+        <v>0.804221</v>
       </c>
       <c r="D41">
-        <v>0.973903</v>
+        <v>0.978016</v>
       </c>
     </row>
     <row r="42">
@@ -8036,13 +8036,13 @@
         </is>
       </c>
       <c r="B42">
-        <v>-3.616822</v>
+        <v>-4.055789</v>
       </c>
       <c r="C42">
-        <v>1.894100</v>
+        <v>-0.845550</v>
       </c>
       <c r="D42">
-        <v>0.973781</v>
+        <v>0.977901</v>
       </c>
     </row>
     <row r="43">
@@ -8052,13 +8052,13 @@
         </is>
       </c>
       <c r="B43">
-        <v>-4.105913</v>
+        <v>-3.437105</v>
       </c>
       <c r="C43">
-        <v>0.318254</v>
+        <v>-2.375167</v>
       </c>
       <c r="D43">
-        <v>0.973664</v>
+        <v>0.977790</v>
       </c>
     </row>
     <row r="44">
@@ -8068,13 +8068,13 @@
         </is>
       </c>
       <c r="B44">
-        <v>-3.937007</v>
+        <v>-2.274357</v>
       </c>
       <c r="C44">
-        <v>-1.323078</v>
+        <v>-3.545858</v>
       </c>
       <c r="D44">
-        <v>0.973551</v>
+        <v>0.977683</v>
       </c>
     </row>
     <row r="45">
@@ -8084,13 +8084,13 @@
         </is>
       </c>
       <c r="B45">
-        <v>-3.142235</v>
+        <v>-0.751081</v>
       </c>
       <c r="C45">
-        <v>-2.769050</v>
+        <v>-4.179995</v>
       </c>
       <c r="D45">
-        <v>0.973442</v>
+        <v>0.977579</v>
       </c>
     </row>
     <row r="46">
@@ -8100,13 +8100,13 @@
         </is>
       </c>
       <c r="B46">
-        <v>-1.850546</v>
+        <v>0.898910</v>
       </c>
       <c r="C46">
-        <v>-3.795715</v>
+        <v>-4.185580</v>
       </c>
       <c r="D46">
-        <v>0.973336</v>
+        <v>0.977479</v>
       </c>
     </row>
     <row r="47">
@@ -8116,13 +8116,13 @@
         </is>
       </c>
       <c r="B47">
-        <v>-0.263994</v>
+        <v>2.428405</v>
       </c>
       <c r="C47">
-        <v>-4.248875</v>
+        <v>-3.566592</v>
       </c>
       <c r="D47">
-        <v>0.973234</v>
+        <v>0.977382</v>
       </c>
     </row>
     <row r="48">
@@ -8132,13 +8132,13 @@
         </is>
       </c>
       <c r="B48">
-        <v>1.375680</v>
+        <v>3.613635</v>
       </c>
       <c r="C48">
-        <v>-4.064574</v>
+        <v>-2.418668</v>
       </c>
       <c r="D48">
-        <v>0.973135</v>
+        <v>0.977287</v>
       </c>
     </row>
     <row r="49">
@@ -8148,13 +8148,13 @@
         </is>
       </c>
       <c r="B49">
-        <v>2.824523</v>
+        <v>4.285739</v>
       </c>
       <c r="C49">
-        <v>-3.275047</v>
+        <v>-0.911759</v>
       </c>
       <c r="D49">
-        <v>0.973039</v>
+        <v>0.977196</v>
       </c>
     </row>
     <row r="50">
@@ -8164,13 +8164,13 @@
         </is>
       </c>
       <c r="B50">
-        <v>3.872122</v>
+        <v>4.352747</v>
       </c>
       <c r="C50">
-        <v>-2.000277</v>
+        <v>0.736880</v>
       </c>
       <c r="D50">
-        <v>0.972946</v>
+        <v>0.977108</v>
       </c>
     </row>
     <row r="51">
@@ -8180,13 +8180,13 @@
         </is>
       </c>
       <c r="B51">
-        <v>4.370621</v>
+        <v>3.809620</v>
       </c>
       <c r="C51">
-        <v>-0.427382</v>
+        <v>2.294928</v>
       </c>
       <c r="D51">
-        <v>0.972856</v>
+        <v>0.977022</v>
       </c>
     </row>
     <row r="52">
@@ -8196,13 +8196,13 @@
         </is>
       </c>
       <c r="B52">
-        <v>4.253340</v>
+        <v>2.735773</v>
       </c>
       <c r="C52">
-        <v>1.218444</v>
+        <v>3.547666</v>
       </c>
       <c r="D52">
-        <v>0.972769</v>
+        <v>0.976939</v>
       </c>
     </row>
     <row r="53">
@@ -8212,13 +8212,13 @@
         </is>
       </c>
       <c r="B53">
-        <v>3.541083</v>
+        <v>1.281201</v>
       </c>
       <c r="C53">
-        <v>2.706795</v>
+        <v>4.326588</v>
       </c>
       <c r="D53">
-        <v>0.972684</v>
+        <v>0.976858</v>
       </c>
     </row>
     <row r="54">
@@ -8228,13 +8228,13 @@
         </is>
       </c>
       <c r="B54">
-        <v>2.336085</v>
+        <v>-0.356165</v>
       </c>
       <c r="C54">
-        <v>3.833952</v>
+        <v>4.530389</v>
       </c>
       <c r="D54">
-        <v>0.972602</v>
+        <v>0.976779</v>
       </c>
     </row>
     <row r="55">
@@ -8244,13 +8244,13 @@
         </is>
       </c>
       <c r="B55">
-        <v>0.805226</v>
+        <v>-1.958340</v>
       </c>
       <c r="C55">
-        <v>4.449556</v>
+        <v>4.136012</v>
       </c>
       <c r="D55">
-        <v>0.972523</v>
+        <v>0.976703</v>
       </c>
     </row>
     <row r="56">
@@ -8260,13 +8260,13 @@
         </is>
       </c>
       <c r="B56">
-        <v>-0.844581</v>
+        <v>-3.316437</v>
       </c>
       <c r="C56">
-        <v>4.474823</v>
+        <v>3.198957</v>
       </c>
       <c r="D56">
-        <v>0.972445</v>
+        <v>0.976629</v>
       </c>
     </row>
     <row r="57">
@@ -8276,13 +8276,13 @@
         </is>
       </c>
       <c r="B57">
-        <v>-2.395053</v>
+        <v>-4.257244</v>
       </c>
       <c r="C57">
-        <v>3.910433</v>
+        <v>1.843455</v>
       </c>
       <c r="D57">
-        <v>0.972370</v>
+        <v>0.976557</v>
       </c>
     </row>
     <row r="58">
@@ -8292,13 +8292,13 @@
         </is>
       </c>
       <c r="B58">
-        <v>-3.645311</v>
+        <v>-4.664019</v>
       </c>
       <c r="C58">
-        <v>2.833700</v>
+        <v>0.244383</v>
       </c>
       <c r="D58">
-        <v>0.972296</v>
+        <v>0.976487</v>
       </c>
     </row>
     <row r="59">
@@ -8308,13 +8308,13 @@
         </is>
       </c>
       <c r="B59">
-        <v>-4.437043</v>
+        <v>-4.489251</v>
       </c>
       <c r="C59">
-        <v>1.386061</v>
+        <v>-1.396335</v>
       </c>
       <c r="D59">
-        <v>0.972225</v>
+        <v>0.976418</v>
       </c>
     </row>
     <row r="60">
@@ -8324,13 +8324,13 @@
         </is>
       </c>
       <c r="B60">
-        <v>-4.673100</v>
+        <v>-3.758259</v>
       </c>
       <c r="C60">
-        <v>-0.246966</v>
+        <v>-2.875575</v>
       </c>
       <c r="D60">
-        <v>0.972156</v>
+        <v>0.976352</v>
       </c>
     </row>
     <row r="61">
@@ -8340,13 +8340,13 @@
         </is>
       </c>
       <c r="B61">
-        <v>-4.327602</v>
+        <v>-2.563750</v>
       </c>
       <c r="C61">
-        <v>-1.860388</v>
+        <v>-4.013841</v>
       </c>
       <c r="D61">
-        <v>0.972088</v>
+        <v>0.976287</v>
       </c>
     </row>
     <row r="62">
@@ -8356,13 +8356,13 @@
         </is>
       </c>
       <c r="B62">
-        <v>-3.446796</v>
+        <v>-1.052503</v>
       </c>
       <c r="C62">
-        <v>-3.255624</v>
+        <v>-4.676135</v>
       </c>
       <c r="D62">
-        <v>0.972023</v>
+        <v>0.976224</v>
       </c>
     </row>
     <row r="63">
@@ -8372,13 +8372,13 @@
         </is>
       </c>
       <c r="B63">
-        <v>-2.141116</v>
+        <v>0.593794</v>
       </c>
       <c r="C63">
-        <v>-4.264434</v>
+        <v>-4.786613</v>
       </c>
       <c r="D63">
-        <v>0.971959</v>
+        <v>0.976162</v>
       </c>
     </row>
     <row r="64">
@@ -8388,13 +8388,13 @@
         </is>
       </c>
       <c r="B64">
-        <v>-0.569884</v>
+        <v>2.180971</v>
       </c>
       <c r="C64">
-        <v>-4.768152</v>
+        <v>-4.335650</v>
       </c>
       <c r="D64">
-        <v>0.971896</v>
+        <v>0.976103</v>
       </c>
     </row>
     <row r="65">
@@ -8404,13 +8404,13 @@
         </is>
       </c>
       <c r="B65">
-        <v>1.079097</v>
+        <v>3.525281</v>
       </c>
       <c r="C65">
-        <v>-4.710185</v>
+        <v>-3.378921</v>
       </c>
       <c r="D65">
-        <v>0.971836</v>
+        <v>0.976044</v>
       </c>
     </row>
     <row r="66">
@@ -8420,13 +8420,13 @@
         </is>
       </c>
       <c r="B66">
-        <v>2.612409</v>
+        <v>4.474138</v>
       </c>
       <c r="C66">
-        <v>-4.100713</v>
+        <v>-2.029043</v>
       </c>
       <c r="D66">
-        <v>0.971776</v>
+        <v>0.975987</v>
       </c>
     </row>
     <row r="67">
@@ -8436,13 +8436,13 @@
         </is>
       </c>
       <c r="B67">
-        <v>3.853537</v>
+        <v>4.922451</v>
       </c>
       <c r="C67">
-        <v>-3.013469</v>
+        <v>-0.441115</v>
       </c>
       <c r="D67">
-        <v>0.971719</v>
+        <v>0.975931</v>
       </c>
     </row>
     <row r="68">
@@ -8452,13 +8452,13 @@
         </is>
       </c>
       <c r="B68">
-        <v>4.662517</v>
+        <v>4.822979</v>
       </c>
       <c r="C68">
-        <v>-1.575396</v>
+        <v>1.205884</v>
       </c>
       <c r="D68">
-        <v>0.971662</v>
+        <v>0.975877</v>
       </c>
     </row>
     <row r="69">
@@ -8468,13 +8468,13 @@
         </is>
       </c>
       <c r="B69">
-        <v>4.950626</v>
+        <v>4.189849</v>
       </c>
       <c r="C69">
-        <v>0.049255</v>
+        <v>2.729579</v>
       </c>
       <c r="D69">
-        <v>0.971607</v>
+        <v>0.975824</v>
       </c>
     </row>
     <row r="70">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="B70">
-        <v>4.688758</v>
+        <v>3.095244</v>
       </c>
       <c r="C70">
-        <v>1.678343</v>
+        <v>3.964220</v>
       </c>
       <c r="D70">
-        <v>0.971553</v>
+        <v>0.975772</v>
       </c>
     </row>
     <row r="71">
@@ -8500,13 +8500,13 @@
         </is>
       </c>
       <c r="B71">
-        <v>3.908894</v>
+        <v>1.659943</v>
       </c>
       <c r="C71">
-        <v>3.132410</v>
+        <v>4.778106</v>
       </c>
       <c r="D71">
-        <v>0.971501</v>
+        <v>0.975721</v>
       </c>
     </row>
     <row r="72">
@@ -8516,13 +8516,13 @@
         </is>
       </c>
       <c r="B72">
-        <v>2.698852</v>
+        <v>0.039053</v>
       </c>
       <c r="C72">
-        <v>4.254148</v>
+        <v>5.086678</v>
       </c>
       <c r="D72">
-        <v>0.971450</v>
+        <v>0.975672</v>
       </c>
     </row>
     <row r="73">
@@ -8532,13 +8532,13 @@
         </is>
       </c>
       <c r="B73">
-        <v>1.191249</v>
+        <v>-1.595320</v>
       </c>
       <c r="C73">
-        <v>4.924696</v>
+        <v>4.860131</v>
       </c>
       <c r="D73">
-        <v>0.971400</v>
+        <v>0.975624</v>
       </c>
     </row>
     <row r="74">
@@ -8548,13 +8548,13 @@
         </is>
       </c>
       <c r="B74">
-        <v>-0.451873</v>
+        <v>-3.072511</v>
       </c>
       <c r="C74">
-        <v>5.075197</v>
+        <v>4.125006</v>
       </c>
       <c r="D74">
-        <v>0.971351</v>
+        <v>0.975576</v>
       </c>
     </row>
     <row r="75">
@@ -8564,13 +8564,13 @@
         </is>
       </c>
       <c r="B75">
-        <v>-2.056916</v>
+        <v>-4.240870</v>
       </c>
       <c r="C75">
-        <v>4.692654</v>
+        <v>2.959915</v>
       </c>
       <c r="D75">
-        <v>0.971303</v>
+        <v>0.975530</v>
       </c>
     </row>
     <row r="76">
@@ -8580,13 +8580,13 @@
         </is>
       </c>
       <c r="B76">
-        <v>-3.457103</v>
+        <v>-4.982735</v>
       </c>
       <c r="C76">
-        <v>3.819742</v>
+        <v>1.486098</v>
       </c>
       <c r="D76">
-        <v>0.971256</v>
+        <v>0.975485</v>
       </c>
     </row>
     <row r="77">
@@ -8596,13 +8596,13 @@
         </is>
       </c>
       <c r="B77">
-        <v>-4.509456</v>
+        <v>-5.225406</v>
       </c>
       <c r="C77">
-        <v>2.548894</v>
+        <v>-0.145959</v>
       </c>
       <c r="D77">
-        <v>0.971210</v>
+        <v>0.975440</v>
       </c>
     </row>
     <row r="78">
@@ -8612,13 +8612,13 @@
         </is>
       </c>
       <c r="B78">
-        <v>-5.108704</v>
+        <v>-4.947223</v>
       </c>
       <c r="C78">
-        <v>1.011558</v>
+        <v>-1.772340</v>
       </c>
       <c r="D78">
-        <v>0.971166</v>
+        <v>0.975397</v>
       </c>
     </row>
     <row r="79">
@@ -8628,13 +8628,13 @@
         </is>
       </c>
       <c r="B79">
-        <v>-5.196878</v>
+        <v>-4.178366</v>
       </c>
       <c r="C79">
-        <v>-0.636084</v>
+        <v>-3.232257</v>
       </c>
       <c r="D79">
-        <v>0.971122</v>
+        <v>0.975355</v>
       </c>
     </row>
     <row r="80">
@@ -8644,13 +8644,13 @@
         </is>
       </c>
       <c r="B80">
-        <v>-4.767838</v>
+        <v>-2.996559</v>
       </c>
       <c r="C80">
-        <v>-2.229327</v>
+        <v>-4.383705</v>
       </c>
       <c r="D80">
-        <v>0.971079</v>
+        <v>0.975313</v>
       </c>
     </row>
     <row r="81">
@@ -8660,13 +8660,13 @@
         </is>
       </c>
       <c r="B81">
-        <v>-3.866520</v>
+        <v>-1.518325</v>
       </c>
       <c r="C81">
-        <v>-3.611401</v>
+        <v>-5.116729</v>
       </c>
       <c r="D81">
-        <v>0.971037</v>
+        <v>0.975272</v>
       </c>
     </row>
     <row r="82">
@@ -8676,13 +8676,13 @@
         </is>
       </c>
       <c r="B82">
-        <v>-2.583239</v>
+        <v>0.113170</v>
       </c>
       <c r="C82">
-        <v>-4.648556</v>
+        <v>-5.363153</v>
       </c>
       <c r="D82">
-        <v>0.970996</v>
+        <v>0.975233</v>
       </c>
     </row>
     <row r="83">
@@ -8692,13 +8692,13 @@
         </is>
       </c>
       <c r="B83">
-        <v>-1.043804</v>
+        <v>1.742371</v>
       </c>
       <c r="C83">
-        <v>-5.242391</v>
+        <v>-5.101993</v>
       </c>
       <c r="D83">
-        <v>0.970956</v>
+        <v>0.975194</v>
       </c>
     </row>
     <row r="84">
@@ -8708,13 +8708,13 @@
         </is>
       </c>
       <c r="B84">
-        <v>0.603402</v>
+        <v>3.216254</v>
       </c>
       <c r="C84">
-        <v>-5.338359</v>
+        <v>-4.360260</v>
       </c>
       <c r="D84">
-        <v>0.970916</v>
+        <v>0.975155</v>
       </c>
     </row>
     <row r="85">
@@ -8724,13 +8724,13 @@
         </is>
       </c>
       <c r="B85">
-        <v>2.202028</v>
+        <v>4.398496</v>
       </c>
       <c r="C85">
-        <v>-4.929829</v>
+        <v>-3.209258</v>
       </c>
       <c r="D85">
-        <v>0.970877</v>
+        <v>0.975118</v>
       </c>
     </row>
     <row r="86">
@@ -8740,13 +8740,13 @@
         </is>
       </c>
       <c r="B86">
-        <v>3.602589</v>
+        <v>5.181620</v>
       </c>
       <c r="C86">
-        <v>-4.057518</v>
+        <v>-1.756945</v>
       </c>
       <c r="D86">
-        <v>0.970840</v>
+        <v>0.975081</v>
       </c>
     </row>
     <row r="87">
@@ -8756,13 +8756,13 @@
         </is>
       </c>
       <c r="B87">
-        <v>4.676168</v>
+        <v>5.496103</v>
       </c>
       <c r="C87">
-        <v>-2.804550</v>
+        <v>-0.137191</v>
       </c>
       <c r="D87">
-        <v>0.970802</v>
+        <v>0.975045</v>
       </c>
     </row>
     <row r="88">
@@ -8772,13 +8772,13 @@
         </is>
       </c>
       <c r="B88">
-        <v>5.325746</v>
+        <v>5.315743</v>
       </c>
       <c r="C88">
-        <v>-1.287794</v>
+        <v>1.502921</v>
       </c>
       <c r="D88">
-        <v>0.970766</v>
+        <v>0.975010</v>
       </c>
     </row>
     <row r="89">
@@ -8788,13 +8788,13 @@
         </is>
       </c>
       <c r="B89">
-        <v>5.494260</v>
+        <v>4.658976</v>
       </c>
       <c r="C89">
-        <v>0.353578</v>
+        <v>3.016578</v>
       </c>
       <c r="D89">
-        <v>0.970730</v>
+        <v>0.974975</v>
       </c>
     </row>
     <row r="90">
@@ -8804,13 +8804,13 @@
         </is>
       </c>
       <c r="B90">
-        <v>5.168787</v>
+        <v>3.586199</v>
       </c>
       <c r="C90">
-        <v>1.971159</v>
+        <v>4.270232</v>
       </c>
       <c r="D90">
-        <v>0.970695</v>
+        <v>0.974941</v>
       </c>
     </row>
     <row r="91">
@@ -8820,13 +8820,13 @@
         </is>
       </c>
       <c r="B91">
-        <v>4.380654</v>
+        <v>2.193484</v>
       </c>
       <c r="C91">
-        <v>3.420761</v>
+        <v>5.155019</v>
       </c>
       <c r="D91">
-        <v>0.970661</v>
+        <v>0.974907</v>
       </c>
     </row>
     <row r="92">
@@ -8836,13 +8836,13 @@
         </is>
       </c>
       <c r="B92">
-        <v>3.201632</v>
+        <v>0.603409</v>
       </c>
       <c r="C92">
-        <v>4.575061</v>
+        <v>5.595657</v>
       </c>
       <c r="D92">
-        <v>0.970627</v>
+        <v>0.974875</v>
       </c>
     </row>
     <row r="93">
@@ -8852,13 +8852,13 @@
         </is>
       </c>
       <c r="B93">
-        <v>1.736718</v>
+        <v>-1.046118</v>
       </c>
       <c r="C93">
-        <v>5.334354</v>
+        <v>5.556166</v>
       </c>
       <c r="D93">
-        <v>0.970594</v>
+        <v>0.974842</v>
       </c>
     </row>
     <row r="94">
@@ -8868,13 +8868,13 @@
         </is>
       </c>
       <c r="B94">
-        <v>0.114259</v>
+        <v>-2.613979</v>
       </c>
       <c r="C94">
-        <v>5.634567</v>
+        <v>5.042055</v>
       </c>
       <c r="D94">
-        <v>0.970562</v>
+        <v>0.974811</v>
       </c>
     </row>
     <row r="95">
@@ -8884,13 +8884,13 @@
         </is>
       </c>
       <c r="B95">
-        <v>-1.525604</v>
+        <v>-3.967861</v>
       </c>
       <c r="C95">
-        <v>5.451954</v>
+        <v>4.098920</v>
       </c>
       <c r="D95">
-        <v>0.970530</v>
+        <v>0.974780</v>
       </c>
     </row>
     <row r="96">
@@ -8900,13 +8900,13 @@
         </is>
       </c>
       <c r="B96">
-        <v>-3.043143</v>
+        <v>-4.995153</v>
       </c>
       <c r="C96">
-        <v>4.804207</v>
+        <v>2.807730</v>
       </c>
       <c r="D96">
-        <v>0.970499</v>
+        <v>0.974749</v>
       </c>
     </row>
     <row r="97">
@@ -8916,13 +8916,13 @@
         </is>
       </c>
       <c r="B97">
-        <v>-4.310822</v>
+        <v>-5.611879</v>
       </c>
       <c r="C97">
-        <v>3.748039</v>
+        <v>1.277322</v>
       </c>
       <c r="D97">
-        <v>0.970468</v>
+        <v>0.974719</v>
       </c>
     </row>
     <row r="98">
@@ -8932,13 +8932,13 @@
         </is>
       </c>
       <c r="B98">
-        <v>-5.223694</v>
+        <v>-5.768987</v>
       </c>
       <c r="C98">
-        <v>2.373570</v>
+        <v>-0.365181</v>
       </c>
       <c r="D98">
-        <v>0.970438</v>
+        <v>0.974690</v>
       </c>
     </row>
     <row r="99">
@@ -8948,13 +8948,13 @@
         </is>
       </c>
       <c r="B99">
-        <v>-5.707612</v>
+        <v>-5.455601</v>
       </c>
       <c r="C99">
-        <v>0.796128</v>
+        <v>-1.985147</v>
       </c>
       <c r="D99">
-        <v>0.970408</v>
+        <v>0.974661</v>
       </c>
     </row>
     <row r="100">
@@ -8964,13 +8964,13 @@
         </is>
       </c>
       <c r="B100">
-        <v>-5.724642</v>
+        <v>-4.699082</v>
       </c>
       <c r="C100">
-        <v>-0.853784</v>
+        <v>-3.451496</v>
       </c>
       <c r="D100">
-        <v>0.970379</v>
+        <v>0.974633</v>
       </c>
     </row>
     <row r="101">
@@ -8980,13 +8980,13 @@
         </is>
       </c>
       <c r="B101">
-        <v>-5.275381</v>
+        <v>-3.562020</v>
       </c>
       <c r="C101">
-        <v>-2.441444</v>
+        <v>-4.647151</v>
       </c>
       <c r="D101">
-        <v>0.970350</v>
+        <v>0.974605</v>
       </c>
     </row>
     <row r="102">
@@ -8996,13 +8996,13 @@
         </is>
       </c>
       <c r="B102">
-        <v>-4.398076</v>
+        <v>-2.136506</v>
       </c>
       <c r="C102">
-        <v>-3.838883</v>
+        <v>-5.478060</v>
       </c>
       <c r="D102">
-        <v>0.970322</v>
+        <v>0.974577</v>
       </c>
     </row>
     <row r="103">
@@ -9012,13 +9012,13 @@
         </is>
       </c>
       <c r="B103">
-        <v>-3.164769</v>
+        <v>-0.536246</v>
       </c>
       <c r="C103">
-        <v>-4.934991</v>
+        <v>-5.880138</v>
       </c>
       <c r="D103">
-        <v>0.970295</v>
+        <v>0.974550</v>
       </c>
     </row>
     <row r="104">
@@ -9028,13 +9028,13 @@
         </is>
       </c>
       <c r="B104">
-        <v>-1.674859</v>
+        <v>1.112787</v>
       </c>
       <c r="C104">
-        <v>-5.643983</v>
+        <v>-5.823664</v>
       </c>
       <c r="D104">
-        <v>0.970267</v>
+        <v>0.974524</v>
       </c>
     </row>
     <row r="105">
@@ -9044,13 +9044,13 @@
         </is>
       </c>
       <c r="B105">
-        <v>-0.046710</v>
+        <v>2.682385</v>
       </c>
       <c r="C105">
-        <v>-5.911624</v>
+        <v>-5.314879</v>
       </c>
       <c r="D105">
-        <v>0.970241</v>
+        <v>0.974498</v>
       </c>
     </row>
     <row r="106">
@@ -9060,13 +9060,13 @@
         </is>
       </c>
       <c r="B106">
-        <v>1.591986</v>
+        <v>4.052021</v>
       </c>
       <c r="C106">
-        <v>-5.718814</v>
+        <v>-4.394772</v>
       </c>
       <c r="D106">
-        <v>0.970214</v>
+        <v>0.974472</v>
       </c>
     </row>
     <row r="107">
@@ -9076,13 +9076,13 @@
         </is>
       </c>
       <c r="B107">
-        <v>3.114289</v>
+        <v>5.117899</v>
       </c>
       <c r="C107">
-        <v>-5.082345</v>
+        <v>-3.135246</v>
       </c>
       <c r="D107">
-        <v>0.970189</v>
+        <v>0.974447</v>
       </c>
     </row>
     <row r="108">
@@ -9092,13 +9092,13 @@
         </is>
       </c>
       <c r="B108">
-        <v>4.403745</v>
+        <v>5.800478</v>
       </c>
       <c r="C108">
-        <v>-4.052878</v>
+        <v>-1.633052</v>
       </c>
       <c r="D108">
-        <v>0.970163</v>
+        <v>0.974422</v>
       </c>
     </row>
     <row r="109">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="B109">
-        <v>5.363046</v>
+        <v>6.049970</v>
       </c>
       <c r="C109">
-        <v>-2.710402</v>
+        <v>-0.002024</v>
       </c>
       <c r="D109">
-        <v>0.970138</v>
+        <v>0.974398</v>
       </c>
     </row>
     <row r="110">
@@ -9124,13 +9124,13 @@
         </is>
       </c>
       <c r="B110">
-        <v>5.921000</v>
+        <v>5.849462</v>
       </c>
       <c r="C110">
-        <v>-1.157602</v>
+        <v>1.635748</v>
       </c>
       <c r="D110">
-        <v>0.970113</v>
+        <v>0.974374</v>
       </c>
     </row>
     <row r="111">
@@ -9140,13 +9140,13 @@
         </is>
       </c>
       <c r="B111">
-        <v>6.037350</v>
+        <v>5.215521</v>
       </c>
       <c r="C111">
-        <v>0.488290</v>
+        <v>3.159105</v>
       </c>
       <c r="D111">
-        <v>0.970089</v>
+        <v>0.974350</v>
       </c>
     </row>
     <row r="112">
@@ -9156,13 +9156,13 @@
         </is>
       </c>
       <c r="B112">
-        <v>5.705158</v>
+        <v>4.196329</v>
       </c>
       <c r="C112">
-        <v>2.104505</v>
+        <v>4.456698</v>
       </c>
       <c r="D112">
-        <v>0.970065</v>
+        <v>0.974327</v>
       </c>
     </row>
     <row r="113">
@@ -9172,13 +9172,13 @@
         </is>
       </c>
       <c r="B113">
-        <v>4.950662</v>
+        <v>2.867562</v>
       </c>
       <c r="C113">
-        <v>3.571895</v>
+        <v>5.434900</v>
       </c>
       <c r="D113">
-        <v>0.970042</v>
+        <v>0.974304</v>
       </c>
     </row>
     <row r="114">
@@ -9188,13 +9188,13 @@
         </is>
       </c>
       <c r="B114">
-        <v>3.830717</v>
+        <v>1.326399</v>
       </c>
       <c r="C114">
-        <v>4.783598</v>
+        <v>6.024236</v>
       </c>
       <c r="D114">
-        <v>0.970019</v>
+        <v>0.974281</v>
       </c>
     </row>
     <row r="115">
@@ -9204,13 +9204,13 @@
         </is>
       </c>
       <c r="B115">
-        <v>2.428072</v>
+        <v>-0.315857</v>
       </c>
       <c r="C115">
-        <v>5.652556</v>
+        <v>6.183906</v>
       </c>
       <c r="D115">
-        <v>0.969996</v>
+        <v>0.974259</v>
       </c>
     </row>
     <row r="116">
@@ -9220,13 +9220,13 @@
         </is>
       </c>
       <c r="B116">
-        <v>0.844909</v>
+        <v>-1.941967</v>
       </c>
       <c r="C116">
-        <v>6.117414</v>
+        <v>5.904144</v>
       </c>
       <c r="D116">
-        <v>0.969974</v>
+        <v>0.974237</v>
       </c>
     </row>
     <row r="117">
@@ -9236,13 +9236,13 @@
         </is>
       </c>
       <c r="B117">
-        <v>-0.804836</v>
+        <v>-3.437145</v>
       </c>
       <c r="C117">
-        <v>6.146427</v>
+        <v>5.206331</v>
       </c>
       <c r="D117">
-        <v>0.969952</v>
+        <v>0.974215</v>
       </c>
     </row>
     <row r="118">
@@ -9252,13 +9252,13 @@
         </is>
       </c>
       <c r="B118">
-        <v>-2.403782</v>
+        <v>-4.697059</v>
       </c>
       <c r="C118">
-        <v>5.739151</v>
+        <v>4.140913</v>
       </c>
       <c r="D118">
-        <v>0.969930</v>
+        <v>0.974194</v>
       </c>
     </row>
     <row r="119">
@@ -9268,13 +9268,13 @@
         </is>
       </c>
       <c r="B119">
-        <v>-3.839439</v>
+        <v>-5.634902</v>
       </c>
       <c r="C119">
-        <v>4.925893</v>
+        <v>2.783359</v>
       </c>
       <c r="D119">
-        <v>0.969909</v>
+        <v>0.974173</v>
       </c>
     </row>
     <row r="120">
@@ -9284,13 +9284,13 @@
         </is>
       </c>
       <c r="B120">
-        <v>-5.011988</v>
+        <v>-6.187058</v>
       </c>
       <c r="C120">
-        <v>3.765019</v>
+        <v>1.228488</v>
       </c>
       <c r="D120">
-        <v>0.969888</v>
+        <v>0.974152</v>
       </c>
     </row>
     <row r="121">
@@ -9300,13 +9300,13 @@
         </is>
       </c>
       <c r="B121">
-        <v>-5.840977</v>
+        <v>-6.317054</v>
       </c>
       <c r="C121">
-        <v>2.338388</v>
+        <v>-0.416383</v>
       </c>
       <c r="D121">
-        <v>0.969867</v>
+        <v>0.974132</v>
       </c>
     </row>
     <row r="122">
@@ -9316,13 +9316,13 @@
         </is>
       </c>
       <c r="B122">
-        <v>-6.270510</v>
+        <v>-6.017541</v>
       </c>
       <c r="C122">
-        <v>0.745277</v>
+        <v>-2.038971</v>
       </c>
       <c r="D122">
-        <v>0.969846</v>
+        <v>0.974112</v>
       </c>
     </row>
     <row r="123">
@@ -9332,13 +9332,13 @@
         </is>
       </c>
       <c r="B123">
-        <v>-6.272629</v>
+        <v>-5.310278</v>
       </c>
       <c r="C123">
-        <v>-0.904722</v>
+        <v>-3.529702</v>
       </c>
       <c r="D123">
-        <v>0.969826</v>
+        <v>0.974092</v>
       </c>
     </row>
     <row r="124">
@@ -9348,13 +9348,13 @@
         </is>
       </c>
       <c r="B124">
-        <v>-5.848708</v>
+        <v>-4.244151</v>
       </c>
       <c r="C124">
-        <v>-2.499335</v>
+        <v>-4.789017</v>
       </c>
       <c r="D124">
-        <v>0.969806</v>
+        <v>0.974073</v>
       </c>
     </row>
     <row r="125">
@@ -9364,13 +9364,13 @@
         </is>
       </c>
       <c r="B125">
-        <v>-5.028835</v>
+        <v>-2.891436</v>
       </c>
       <c r="C125">
-        <v>-3.931225</v>
+        <v>-5.733824</v>
       </c>
       <c r="D125">
-        <v>0.969787</v>
+        <v>0.974054</v>
       </c>
     </row>
     <row r="126">
@@ -9380,13 +9380,13 @@
         </is>
       </c>
       <c r="B126">
-        <v>-3.869292</v>
+        <v>-1.342609</v>
       </c>
       <c r="C126">
-        <v>-5.105089</v>
+        <v>-6.302712</v>
       </c>
       <c r="D126">
-        <v>0.969767</v>
+        <v>0.974035</v>
       </c>
     </row>
     <row r="127">
@@ -9396,13 +9396,13 @@
         </is>
       </c>
       <c r="B127">
-        <v>-2.448346</v>
+        <v>0.299915</v>
       </c>
       <c r="C127">
-        <v>-5.943787</v>
+        <v>-6.459603</v>
       </c>
       <c r="D127">
-        <v>0.969748</v>
+        <v>0.974016</v>
       </c>
     </row>
     <row r="128">
@@ -9412,13 +9412,13 @@
         </is>
       </c>
       <c r="B128">
-        <v>-0.860703</v>
+        <v>1.928669</v>
       </c>
       <c r="C128">
-        <v>-6.393108</v>
+        <v>-6.195666</v>
       </c>
       <c r="D128">
-        <v>0.969730</v>
+        <v>0.973998</v>
       </c>
     </row>
     <row r="129">
@@ -9428,13 +9428,13 @@
         </is>
       </c>
       <c r="B129">
-        <v>0.788990</v>
+        <v>3.438181</v>
       </c>
       <c r="C129">
-        <v>-6.424933</v>
+        <v>-5.529428</v>
       </c>
       <c r="D129">
-        <v>0.969711</v>
+        <v>0.973980</v>
       </c>
     </row>
     <row r="130">
@@ -9444,13 +9444,13 @@
         </is>
       </c>
       <c r="B130">
-        <v>2.393127</v>
+        <v>4.731730</v>
       </c>
       <c r="C130">
-        <v>-6.038612</v>
+        <v>-4.505109</v>
       </c>
       <c r="D130">
-        <v>0.969693</v>
+        <v>0.973962</v>
       </c>
     </row>
     <row r="131">
@@ -9460,13 +9460,13 @@
         </is>
       </c>
       <c r="B131">
-        <v>3.848152</v>
+        <v>5.727377</v>
       </c>
       <c r="C131">
-        <v>-5.260536</v>
+        <v>-3.189363</v>
       </c>
       <c r="D131">
-        <v>0.969675</v>
+        <v>0.973944</v>
       </c>
     </row>
     <row r="132">
@@ -9476,13 +9476,13 @@
         </is>
       </c>
       <c r="B132">
-        <v>5.061138</v>
+        <v>6.362916</v>
       </c>
       <c r="C132">
-        <v>-4.141981</v>
+        <v>-1.666671</v>
       </c>
       <c r="D132">
-        <v>0.969657</v>
+        <v>0.973927</v>
       </c>
     </row>
     <row r="133">
@@ -9492,13 +9492,13 @@
         </is>
       </c>
       <c r="B133">
-        <v>5.955535</v>
+        <v>6.599467</v>
       </c>
       <c r="C133">
-        <v>-2.755419</v>
+        <v>-0.033716</v>
       </c>
       <c r="D133">
-        <v>0.969640</v>
+        <v>0.973909</v>
       </c>
     </row>
     <row r="134">
@@ -9508,13 +9508,13 @@
         </is>
       </c>
       <c r="B134">
-        <v>6.475744</v>
+        <v>6.423522</v>
       </c>
       <c r="C134">
-        <v>-1.189570</v>
+        <v>1.606877</v>
       </c>
       <c r="D134">
-        <v>0.969622</v>
+        <v>0.973892</v>
       </c>
     </row>
     <row r="135">
@@ -9524,13 +9524,13 @@
         </is>
       </c>
       <c r="B135">
-        <v>6.590265</v>
+        <v>5.847373</v>
       </c>
       <c r="C135">
-        <v>0.456451</v>
+        <v>3.153017</v>
       </c>
       <c r="D135">
-        <v>0.969605</v>
+        <v>0.973876</v>
       </c>
     </row>
     <row r="136">
@@ -9540,13 +9540,13 @@
         </is>
       </c>
       <c r="B136">
-        <v>6.293267</v>
+        <v>4.907919</v>
       </c>
       <c r="C136">
-        <v>2.079501</v>
+        <v>4.509457</v>
       </c>
       <c r="D136">
-        <v>0.969589</v>
+        <v>0.973859</v>
       </c>
     </row>
     <row r="137">
@@ -9556,13 +9556,13 @@
         </is>
       </c>
       <c r="B137">
-        <v>5.604528</v>
+        <v>3.664012</v>
       </c>
       <c r="C137">
-        <v>3.578881</v>
+        <v>5.593520</v>
       </c>
       <c r="D137">
-        <v>0.969572</v>
+        <v>0.973843</v>
       </c>
     </row>
     <row r="138">
@@ -9572,13 +9572,13 @@
         </is>
       </c>
       <c r="B138">
-        <v>4.567797</v>
+        <v>2.192501</v>
       </c>
       <c r="C138">
-        <v>4.862504</v>
+        <v>6.339950</v>
       </c>
       <c r="D138">
-        <v>0.969556</v>
+        <v>0.973827</v>
       </c>
     </row>
     <row r="139">
@@ -9588,13 +9588,13 @@
         </is>
       </c>
       <c r="B139">
-        <v>3.247720</v>
+        <v>0.583295</v>
       </c>
       <c r="C139">
-        <v>5.852402</v>
+        <v>6.704578</v>
       </c>
       <c r="D139">
-        <v>0.969539</v>
+        <v>0.973811</v>
       </c>
     </row>
     <row r="140">
@@ -9604,13 +9604,13 @@
         </is>
       </c>
       <c r="B140">
-        <v>1.725572</v>
+        <v>-1.066269</v>
       </c>
       <c r="C140">
-        <v>6.489242</v>
+        <v>6.666651</v>
       </c>
       <c r="D140">
-        <v>0.969523</v>
+        <v>0.973795</v>
       </c>
     </row>
     <row r="141">
@@ -9620,13 +9620,13 @@
         </is>
       </c>
       <c r="B141">
-        <v>0.094070</v>
+        <v>-2.657361</v>
       </c>
       <c r="C141">
-        <v>6.735621</v>
+        <v>6.229700</v>
       </c>
       <c r="D141">
-        <v>0.969508</v>
+        <v>0.973780</v>
       </c>
     </row>
     <row r="142">
@@ -9636,13 +9636,13 @@
         </is>
       </c>
       <c r="B142">
-        <v>-1.548380</v>
+        <v>-4.095561</v>
       </c>
       <c r="C142">
-        <v>6.577957</v>
+        <v>5.420947</v>
       </c>
       <c r="D142">
-        <v>0.969492</v>
+        <v>0.973765</v>
       </c>
     </row>
     <row r="143">
@@ -9652,13 +9652,13 @@
         </is>
       </c>
       <c r="B143">
-        <v>-3.103652</v>
+        <v>-5.296368</v>
       </c>
       <c r="C143">
-        <v>6.026932</v>
+        <v>4.289328</v>
       </c>
       <c r="D143">
-        <v>0.969477</v>
+        <v>0.973749</v>
       </c>
     </row>
     <row r="144">
@@ -9668,13 +9668,13 @@
         </is>
       </c>
       <c r="B144">
-        <v>-4.479717</v>
+        <v>-6.190007</v>
       </c>
       <c r="C144">
-        <v>5.116469</v>
+        <v>2.902277</v>
       </c>
       <c r="D144">
-        <v>0.969462</v>
+        <v>0.973735</v>
       </c>
     </row>
     <row r="145">
@@ -9684,13 +9684,13 @@
         </is>
       </c>
       <c r="B145">
-        <v>-5.595978</v>
+        <v>-6.725273</v>
       </c>
       <c r="C145">
-        <v>3.901372</v>
+        <v>1.341511</v>
       </c>
       <c r="D145">
-        <v>0.969447</v>
+        <v>0.973720</v>
       </c>
     </row>
     <row r="146">
@@ -9700,13 +9700,13 @@
         </is>
       </c>
       <c r="B146">
-        <v>-6.387813</v>
+        <v>-6.872214</v>
       </c>
       <c r="C146">
-        <v>2.453788</v>
+        <v>-0.301933</v>
       </c>
       <c r="D146">
-        <v>0.969432</v>
+        <v>0.973705</v>
       </c>
     </row>
     <row r="147">
@@ -9716,13 +9716,13 @@
         </is>
       </c>
       <c r="B147">
-        <v>-6.810091</v>
+        <v>-6.623534</v>
       </c>
       <c r="C147">
-        <v>0.858739</v>
+        <v>-1.933085</v>
       </c>
       <c r="D147">
-        <v>0.969417</v>
+        <v>0.973691</v>
       </c>
     </row>
     <row r="148">
@@ -9732,13 +9732,13 @@
         </is>
       </c>
       <c r="B148">
-        <v>-6.839491</v>
+        <v>-5.994667</v>
       </c>
       <c r="C148">
-        <v>-0.790999</v>
+        <v>-3.458545</v>
       </c>
       <c r="D148">
-        <v>0.969403</v>
+        <v>0.973677</v>
       </c>
     </row>
     <row r="149">
@@ -9748,13 +9748,13 @@
         </is>
       </c>
       <c r="B149">
-        <v>-6.475505</v>
+        <v>-5.022551</v>
       </c>
       <c r="C149">
-        <v>-2.400351</v>
+        <v>-4.791771</v>
       </c>
       <c r="D149">
-        <v>0.969389</v>
+        <v>0.973663</v>
       </c>
     </row>
     <row r="150">
@@ -9764,13 +9764,13 @@
         </is>
       </c>
       <c r="B150">
-        <v>-5.740125</v>
+        <v>-3.763223</v>
       </c>
       <c r="C150">
-        <v>-3.877415</v>
+        <v>-5.857881</v>
       </c>
       <c r="D150">
-        <v>0.969375</v>
+        <v>0.973649</v>
       </c>
     </row>
     <row r="151">
@@ -9780,13 +9780,13 @@
         </is>
       </c>
       <c r="B151">
-        <v>-4.676253</v>
+        <v>-2.288372</v>
       </c>
       <c r="C151">
-        <v>-5.138635</v>
+        <v>-6.597688</v>
       </c>
       <c r="D151">
-        <v>0.969361</v>
+        <v>0.973635</v>
       </c>
     </row>
     <row r="152">
@@ -9796,13 +9796,13 @@
         </is>
       </c>
       <c r="B152">
-        <v>-3.344963</v>
+        <v>-0.681106</v>
       </c>
       <c r="C152">
-        <v>-6.113400</v>
+        <v>-6.970778</v>
       </c>
       <c r="D152">
-        <v>0.969347</v>
+        <v>0.973622</v>
       </c>
     </row>
     <row r="153">
@@ -9812,13 +9812,13 @@
         </is>
       </c>
       <c r="B153">
-        <v>-1.821802</v>
+        <v>0.968841</v>
       </c>
       <c r="C153">
-        <v>-6.747814</v>
+        <v>-6.957479</v>
       </c>
       <c r="D153">
-        <v>0.969333</v>
+        <v>0.973608</v>
       </c>
     </row>
     <row r="154">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="B154">
-        <v>-0.192359</v>
+        <v>2.570161</v>
       </c>
       <c r="C154">
-        <v>-7.007458</v>
+        <v>-6.559645</v>
       </c>
       <c r="D154">
-        <v>0.969320</v>
+        <v>0.973595</v>
       </c>
     </row>
     <row r="155">
@@ -9844,13 +9844,13 @@
         </is>
       </c>
       <c r="B155">
-        <v>1.452634</v>
+        <v>4.035019</v>
       </c>
       <c r="C155">
-        <v>-6.879014</v>
+        <v>-5.800242</v>
       </c>
       <c r="D155">
-        <v>0.969307</v>
+        <v>0.973582</v>
       </c>
     </row>
     <row r="156">
@@ -9860,13 +9860,13 @@
         </is>
       </c>
       <c r="B156">
-        <v>3.022382</v>
+        <v>5.283790</v>
       </c>
       <c r="C156">
-        <v>-6.370691</v>
+        <v>-4.721785</v>
       </c>
       <c r="D156">
-        <v>0.969294</v>
+        <v>0.973569</v>
       </c>
     </row>
     <row r="157">
@@ -9876,13 +9876,13 @@
         </is>
       </c>
       <c r="B157">
-        <v>4.431006</v>
+        <v>6.249274</v>
       </c>
       <c r="C157">
-        <v>-5.511459</v>
+        <v>-3.383749</v>
       </c>
       <c r="D157">
-        <v>0.969281</v>
+        <v>0.973557</v>
       </c>
     </row>
     <row r="158">
@@ -9892,13 +9892,13 @@
         </is>
       </c>
       <c r="B158">
-        <v>5.602158</v>
+        <v>6.880143</v>
       </c>
       <c r="C158">
-        <v>-4.349176</v>
+        <v>-1.859116</v>
       </c>
       <c r="D158">
-        <v>0.969268</v>
+        <v>0.973544</v>
       </c>
     </row>
     <row r="159">
@@ -9908,13 +9908,13 @@
         </is>
       </c>
       <c r="B159">
-        <v>6.473020</v>
+        <v>7.143469</v>
       </c>
       <c r="C159">
-        <v>-2.947713</v>
+        <v>-0.230264</v>
       </c>
       <c r="D159">
-        <v>0.969255</v>
+        <v>0.973531</v>
       </c>
     </row>
     <row r="160">
@@ -9924,13 +9924,13 @@
         </is>
       </c>
       <c r="B160">
-        <v>6.997500</v>
+        <v>7.026225</v>
       </c>
       <c r="C160">
-        <v>-1.383289</v>
+        <v>1.415565</v>
       </c>
       <c r="D160">
-        <v>0.969243</v>
+        <v>0.973519</v>
       </c>
     </row>
     <row r="161">
@@ -9940,13 +9940,13 @@
         </is>
       </c>
       <c r="B161">
-        <v>7.148461</v>
+        <v>6.535693</v>
       </c>
       <c r="C161">
-        <v>0.259790</v>
+        <v>2.990963</v>
       </c>
       <c r="D161">
-        <v>0.969230</v>
+        <v>0.973507</v>
       </c>
     </row>
     <row r="162">
@@ -9956,13 +9956,13 @@
         </is>
       </c>
       <c r="B162">
-        <v>6.918902</v>
+        <v>5.698799</v>
       </c>
       <c r="C162">
-        <v>1.893744</v>
+        <v>4.412972</v>
       </c>
       <c r="D162">
-        <v>0.969218</v>
+        <v>0.973495</v>
       </c>
     </row>
     <row r="163">
@@ -9972,13 +9972,13 @@
         </is>
       </c>
       <c r="B163">
-        <v>6.322046</v>
+        <v>4.560422</v>
       </c>
       <c r="C163">
-        <v>3.432010</v>
+        <v>5.607375</v>
       </c>
       <c r="D163">
-        <v>0.969206</v>
+        <v>0.973483</v>
       </c>
     </row>
     <row r="164">
@@ -9988,13 +9988,13 @@
         </is>
       </c>
       <c r="B164">
-        <v>5.390358</v>
+        <v>3.180809</v>
       </c>
       <c r="C164">
-        <v>4.793795</v>
+        <v>6.512452</v>
       </c>
       <c r="D164">
-        <v>0.969194</v>
+        <v>0.973471</v>
       </c>
     </row>
     <row r="165">
@@ -10004,13 +10004,13 @@
         </is>
       </c>
       <c r="B165">
-        <v>4.173582</v>
+        <v>1.632228</v>
       </c>
       <c r="C165">
-        <v>5.908225</v>
+        <v>7.082011</v>
       </c>
       <c r="D165">
-        <v>0.969182</v>
+        <v>0.973460</v>
       </c>
     </row>
     <row r="166">
@@ -10020,13 +10020,13 @@
         </is>
       </c>
       <c r="B166">
-        <v>2.735903</v>
+        <v>-0.004919</v>
       </c>
       <c r="C166">
-        <v>6.717903</v>
+        <v>7.287557</v>
       </c>
       <c r="D166">
-        <v>0.969171</v>
+        <v>0.973448</v>
       </c>
     </row>
     <row r="167">
@@ -10036,13 +10036,13 @@
         </is>
       </c>
       <c r="B167">
-        <v>1.152427</v>
+        <v>-1.646340</v>
       </c>
       <c r="C167">
-        <v>7.181697</v>
+        <v>7.119519</v>
       </c>
       <c r="D167">
-        <v>0.969159</v>
+        <v>0.973437</v>
       </c>
     </row>
     <row r="168">
@@ -10052,13 +10052,13 @@
         </is>
       </c>
       <c r="B168">
-        <v>-0.494840</v>
+        <v>-3.208208</v>
       </c>
       <c r="C168">
-        <v>7.276637</v>
+        <v>6.587476</v>
       </c>
       <c r="D168">
-        <v>0.969148</v>
+        <v>0.973426</v>
       </c>
     </row>
     <row r="169">
@@ -10068,13 +10068,13 @@
         </is>
       </c>
       <c r="B169">
-        <v>-2.121288</v>
+        <v>-4.611412</v>
       </c>
       <c r="C169">
-        <v>6.998851</v>
+        <v>5.719421</v>
       </c>
       <c r="D169">
-        <v>0.969137</v>
+        <v>0.973414</v>
       </c>
     </row>
     <row r="170">
@@ -10084,13 +10084,13 @@
         </is>
       </c>
       <c r="B170">
-        <v>-3.644057</v>
+        <v>-5.785490</v>
       </c>
       <c r="C170">
-        <v>6.363497</v>
+        <v>4.560094</v>
       </c>
       <c r="D170">
-        <v>0.969125</v>
+        <v>0.973403</v>
       </c>
     </row>
     <row r="171">
@@ -10100,13 +10100,13 @@
         </is>
       </c>
       <c r="B171">
-        <v>-4.986208</v>
+        <v>-6.672057</v>
       </c>
       <c r="C171">
-        <v>5.403742</v>
+        <v>3.168512</v>
       </c>
       <c r="D171">
-        <v>0.969114</v>
+        <v>0.973392</v>
       </c>
     </row>
     <row r="172">
@@ -10116,13 +10116,13 @@
         </is>
       </c>
       <c r="B172">
-        <v>-6.080530</v>
+        <v>-7.227556</v>
       </c>
       <c r="C172">
-        <v>4.168849</v>
+        <v>1.614833</v>
       </c>
       <c r="D172">
-        <v>0.969103</v>
+        <v>0.973382</v>
       </c>
     </row>
     <row r="173">
@@ -10132,13 +10132,13 @@
         </is>
       </c>
       <c r="B173">
-        <v>-6.872778</v>
+        <v>-7.425238</v>
       </c>
       <c r="C173">
-        <v>2.721492</v>
+        <v>-0.023283</v>
       </c>
       <c r="D173">
-        <v>0.969093</v>
+        <v>0.973371</v>
       </c>
     </row>
     <row r="174">
@@ -10148,13 +10148,13 @@
         </is>
       </c>
       <c r="B174">
-        <v>-7.324212</v>
+        <v>-7.256254</v>
       </c>
       <c r="C174">
-        <v>1.134449</v>
+        <v>-1.664607</v>
       </c>
       <c r="D174">
-        <v>0.969082</v>
+        <v>0.973360</v>
       </c>
     </row>
     <row r="175">
@@ -10164,13 +10164,13 @@
         </is>
       </c>
       <c r="B175">
-        <v>-7.413311</v>
+        <v>-6.729865</v>
       </c>
       <c r="C175">
-        <v>-0.513144</v>
+        <v>-3.228389</v>
       </c>
       <c r="D175">
-        <v>0.969071</v>
+        <v>0.973350</v>
       </c>
     </row>
     <row r="176">
@@ -10180,13 +10180,13 @@
         </is>
       </c>
       <c r="B176">
-        <v>-7.136616</v>
+        <v>-5.872749</v>
       </c>
       <c r="C176">
-        <v>-2.139779</v>
+        <v>-4.638301</v>
       </c>
       <c r="D176">
-        <v>0.969061</v>
+        <v>0.973340</v>
       </c>
     </row>
     <row r="177">
@@ -10196,13 +10196,13 @@
         </is>
       </c>
       <c r="B177">
-        <v>-6.508660</v>
+        <v>-4.727479</v>
       </c>
       <c r="C177">
-        <v>-3.665613</v>
+        <v>-5.826096</v>
       </c>
       <c r="D177">
-        <v>0.969050</v>
+        <v>0.973329</v>
       </c>
     </row>
     <row r="178">
@@ -10212,13 +10212,13 @@
         </is>
       </c>
       <c r="B178">
-        <v>-5.561028</v>
+        <v>-3.350257</v>
       </c>
       <c r="C178">
-        <v>-5.016351</v>
+        <v>-6.734809</v>
       </c>
       <c r="D178">
-        <v>0.969040</v>
+        <v>0.973319</v>
       </c>
     </row>
     <row r="179">
@@ -10228,13 +10228,13 @@
         </is>
       </c>
       <c r="B179">
-        <v>-4.340599</v>
+        <v>-1.808033</v>
       </c>
       <c r="C179">
-        <v>-6.126781</v>
+        <v>-7.321361</v>
       </c>
       <c r="D179">
-        <v>0.969030</v>
+        <v>0.973309</v>
       </c>
     </row>
     <row r="180">
@@ -10244,13 +10244,13 @@
         </is>
       </c>
       <c r="B180">
-        <v>-2.907086</v>
+        <v>-0.175154</v>
       </c>
       <c r="C180">
-        <v>-6.943812</v>
+        <v>-7.558443</v>
       </c>
       <c r="D180">
-        <v>0.969020</v>
+        <v>0.973299</v>
       </c>
     </row>
     <row r="181">
@@ -10260,13 +10260,13 @@
         </is>
       </c>
       <c r="B181">
-        <v>-1.329996</v>
+        <v>1.470268</v>
       </c>
       <c r="C181">
-        <v>-7.428877</v>
+        <v>-7.435622</v>
       </c>
       <c r="D181">
-        <v>0.969010</v>
+        <v>0.973290</v>
       </c>
     </row>
     <row r="182">
@@ -10276,13 +10276,13 @@
         </is>
       </c>
       <c r="B182">
-        <v>0.314818</v>
+        <v>3.050118</v>
       </c>
       <c r="C182">
-        <v>-7.559591</v>
+        <v>-6.959623</v>
       </c>
       <c r="D182">
-        <v>0.969000</v>
+        <v>0.973280</v>
       </c>
     </row>
     <row r="183">
@@ -10292,13 +10292,13 @@
         </is>
       </c>
       <c r="B183">
-        <v>1.948853</v>
+        <v>4.489961</v>
       </c>
       <c r="C183">
-        <v>-7.330615</v>
+        <v>-6.153799</v>
       </c>
       <c r="D183">
-        <v>0.968990</v>
+        <v>0.973270</v>
       </c>
     </row>
     <row r="184">
@@ -10308,13 +10308,13 @@
         </is>
       </c>
       <c r="B184">
-        <v>3.494706</v>
+        <v>5.722496</v>
       </c>
       <c r="C184">
-        <v>-6.753695</v>
+        <v>-5.056822</v>
       </c>
       <c r="D184">
-        <v>0.968981</v>
+        <v>0.973261</v>
       </c>
     </row>
     <row r="185">
@@ -10324,13 +10324,13 @@
         </is>
       </c>
       <c r="B185">
-        <v>4.879713</v>
+        <v>6.690612</v>
       </c>
       <c r="C185">
-        <v>-5.856891</v>
+        <v>-3.720689</v>
       </c>
       <c r="D185">
-        <v>0.968971</v>
+        <v>0.973251</v>
       </c>
     </row>
     <row r="186">
@@ -10340,13 +10340,13 @@
         </is>
       </c>
       <c r="B186">
-        <v>6.039296</v>
+        <v>7.349922</v>
       </c>
       <c r="C186">
-        <v>-4.683065</v>
+        <v>-2.208138</v>
       </c>
       <c r="D186">
-        <v>0.968962</v>
+        <v>0.973242</v>
       </c>
     </row>
     <row r="187">
@@ -10356,13 +10356,13 @@
         </is>
       </c>
       <c r="B187">
-        <v>6.919878</v>
+        <v>7.670658</v>
       </c>
       <c r="C187">
-        <v>-3.287689</v>
+        <v>-0.589612</v>
       </c>
       <c r="D187">
-        <v>0.968952</v>
+        <v>0.973233</v>
       </c>
     </row>
     <row r="188">
@@ -10372,13 +10372,13 @@
         </is>
       </c>
       <c r="B188">
-        <v>7.481237</v>
+        <v>7.638865</v>
       </c>
       <c r="C188">
-        <v>-1.736117</v>
+        <v>1.060082</v>
       </c>
       <c r="D188">
-        <v>0.968943</v>
+        <v>0.973224</v>
       </c>
     </row>
     <row r="189">
@@ -10388,13 +10388,13 @@
         </is>
       </c>
       <c r="B189">
-        <v>7.698203</v>
+        <v>7.256850</v>
       </c>
       <c r="C189">
-        <v>-0.100444</v>
+        <v>2.665250</v>
       </c>
       <c r="D189">
-        <v>0.968934</v>
+        <v>0.973214</v>
       </c>
     </row>
     <row r="190">
@@ -10404,13 +10404,13 @@
         </is>
       </c>
       <c r="B190">
-        <v>7.561627</v>
+        <v>6.542878</v>
       </c>
       <c r="C190">
-        <v>1.543894</v>
+        <v>4.152779</v>
       </c>
       <c r="D190">
-        <v>0.968925</v>
+        <v>0.973206</v>
       </c>
     </row>
     <row r="191">
@@ -10420,13 +10420,13 @@
         </is>
       </c>
       <c r="B191">
-        <v>7.078612</v>
+        <v>5.530151</v>
       </c>
       <c r="C191">
-        <v>3.121613</v>
+        <v>5.455424</v>
       </c>
       <c r="D191">
-        <v>0.968916</v>
+        <v>0.973197</v>
       </c>
     </row>
     <row r="192">
@@ -10436,13 +10436,13 @@
         </is>
       </c>
       <c r="B192">
-        <v>6.271987</v>
+        <v>4.265130</v>
       </c>
       <c r="C192">
-        <v>4.561007</v>
+        <v>6.514774</v>
       </c>
       <c r="D192">
-        <v>0.968907</v>
+        <v>0.973188</v>
       </c>
     </row>
     <row r="193">
@@ -10452,13 +10452,13 @@
         </is>
       </c>
       <c r="B193">
-        <v>5.179088</v>
+        <v>2.805288</v>
       </c>
       <c r="C193">
-        <v>5.797159</v>
+        <v>7.283774</v>
       </c>
       <c r="D193">
-        <v>0.968898</v>
+        <v>0.973179</v>
       </c>
     </row>
     <row r="194">
@@ -10468,13 +10468,13 @@
         </is>
       </c>
       <c r="B194">
-        <v>3.849896</v>
+        <v>1.216406</v>
       </c>
       <c r="C194">
-        <v>6.774784</v>
+        <v>7.728697</v>
       </c>
       <c r="D194">
-        <v>0.968889</v>
+        <v>0.973170</v>
       </c>
     </row>
     <row r="195">
@@ -10484,13 +10484,13 @@
         </is>
       </c>
       <c r="B195">
-        <v>2.344647</v>
+        <v>-0.430451</v>
       </c>
       <c r="C195">
-        <v>7.450598</v>
+        <v>7.830485</v>
       </c>
       <c r="D195">
-        <v>0.968881</v>
+        <v>0.973162</v>
       </c>
     </row>
     <row r="196">
@@ -10500,13 +10500,13 @@
         </is>
       </c>
       <c r="B196">
-        <v>0.731015</v>
+        <v>-2.062151</v>
       </c>
       <c r="C196">
-        <v>7.795113</v>
+        <v>7.585426</v>
       </c>
       <c r="D196">
-        <v>0.968872</v>
+        <v>0.973153</v>
       </c>
     </row>
     <row r="197">
@@ -10516,13 +10516,13 @@
         </is>
       </c>
       <c r="B197">
-        <v>-0.918985</v>
+        <v>-3.606743</v>
       </c>
       <c r="C197">
-        <v>7.793781</v>
+        <v>7.005137</v>
       </c>
       <c r="D197">
-        <v>0.968864</v>
+        <v>0.973145</v>
       </c>
     </row>
     <row r="198">
@@ -10532,13 +10532,13 @@
         </is>
       </c>
       <c r="B198">
-        <v>-2.532231</v>
+        <v>-4.996602</v>
       </c>
       <c r="C198">
-        <v>7.447466</v>
+        <v>6.115872</v>
       </c>
       <c r="D198">
-        <v>0.968855</v>
+        <v>0.973137</v>
       </c>
     </row>
     <row r="199">
@@ -10548,13 +10548,13 @@
         </is>
       </c>
       <c r="B199">
-        <v>-4.037737</v>
+        <v>-6.171335</v>
       </c>
       <c r="C199">
-        <v>6.772223</v>
+        <v>4.957208</v>
       </c>
       <c r="D199">
-        <v>0.968847</v>
+        <v>0.973128</v>
       </c>
     </row>
     <row r="200">
@@ -10564,13 +10564,13 @@
         </is>
       </c>
       <c r="B200">
-        <v>-5.369731</v>
+        <v>-7.080328</v>
       </c>
       <c r="C200">
-        <v>5.798420</v>
+        <v>3.580171</v>
       </c>
       <c r="D200">
-        <v>0.968839</v>
+        <v>0.973120</v>
       </c>
     </row>
     <row r="201">
@@ -10580,13 +10580,13 @@
         </is>
       </c>
       <c r="B201">
-        <v>-6.470475</v>
+        <v>-7.684821</v>
       </c>
       <c r="C201">
-        <v>4.569248</v>
+        <v>2.044889</v>
       </c>
       <c r="D201">
-        <v>0.968830</v>
+        <v>0.973112</v>
       </c>
     </row>
     <row r="202">
@@ -10596,13 +10596,13 @@
         </is>
       </c>
       <c r="B202">
-        <v>-7.292672</v>
+        <v>-7.959445</v>
       </c>
       <c r="C202">
-        <v>3.138692</v>
+        <v>0.417904</v>
       </c>
       <c r="D202">
-        <v>0.968822</v>
+        <v>0.973104</v>
       </c>
     </row>
     <row r="203">
@@ -10612,13 +10612,13 @@
         </is>
       </c>
       <c r="B203">
-        <v>-7.801398</v>
+        <v>-7.893161</v>
       </c>
       <c r="C203">
-        <v>1.569075</v>
+        <v>-1.230764</v>
       </c>
       <c r="D203">
-        <v>0.968814</v>
+        <v>0.973096</v>
       </c>
     </row>
     <row r="204">
@@ -10628,13 +10628,13 @@
         </is>
       </c>
       <c r="B204">
-        <v>-7.975465</v>
+        <v>-7.489566</v>
       </c>
       <c r="C204">
-        <v>-0.071718</v>
+        <v>-2.830643</v>
       </c>
       <c r="D204">
-        <v>0.968806</v>
+        <v>0.973088</v>
       </c>
     </row>
     <row r="205">
@@ -10644,13 +10644,13 @@
         </is>
       </c>
       <c r="B205">
-        <v>-7.808165</v>
+        <v>-6.766576</v>
       </c>
       <c r="C205">
-        <v>-1.713215</v>
+        <v>-4.313810</v>
       </c>
       <c r="D205">
-        <v>0.968798</v>
+        <v>0.973081</v>
       </c>
     </row>
     <row r="206">
@@ -10660,13 +10660,13 @@
         </is>
       </c>
       <c r="B206">
-        <v>-7.307402</v>
+        <v>-5.755505</v>
       </c>
       <c r="C206">
-        <v>-3.285390</v>
+        <v>-5.617741</v>
       </c>
       <c r="D206">
-        <v>0.968791</v>
+        <v>0.973073</v>
       </c>
     </row>
     <row r="207">
@@ -10676,13 +10676,13 @@
         </is>
       </c>
       <c r="B207">
-        <v>-6.495184</v>
+        <v>-4.499602</v>
       </c>
       <c r="C207">
-        <v>-4.721636</v>
+        <v>-6.687884</v>
       </c>
       <c r="D207">
-        <v>0.968783</v>
+        <v>0.973065</v>
       </c>
     </row>
     <row r="208">
@@ -10692,13 +10692,13 @@
         </is>
       </c>
       <c r="B208">
-        <v>-5.406541</v>
+        <v>-3.052095</v>
       </c>
       <c r="C208">
-        <v>-5.961538</v>
+        <v>-7.479859</v>
       </c>
       <c r="D208">
-        <v>0.968775</v>
+        <v>0.973058</v>
       </c>
     </row>
     <row r="209">
@@ -10708,13 +10708,13 @@
         </is>
       </c>
       <c r="B209">
-        <v>-4.087901</v>
+        <v>-1.473864</v>
       </c>
       <c r="C209">
-        <v>-6.953348</v>
+        <v>-7.961196</v>
       </c>
       <c r="D209">
-        <v>0.968768</v>
+        <v>0.973050</v>
       </c>
     </row>
     <row r="210">
@@ -10724,13 +10724,13 @@
         </is>
       </c>
       <c r="B210">
-        <v>-2.595018</v>
+        <v>0.169179</v>
       </c>
       <c r="C210">
-        <v>-7.656058</v>
+        <v>-8.112561</v>
       </c>
       <c r="D210">
-        <v>0.968760</v>
+        <v>0.973043</v>
       </c>
     </row>
     <row r="211">
@@ -10740,13 +10740,13 @@
         </is>
       </c>
       <c r="B211">
-        <v>-0.990547</v>
+        <v>1.808870</v>
       </c>
       <c r="C211">
-        <v>-8.040989</v>
+        <v>-7.928405</v>
       </c>
       <c r="D211">
-        <v>0.968753</v>
+        <v>0.973035</v>
       </c>
     </row>
     <row r="212">
@@ -10756,13 +10756,13 @@
         </is>
       </c>
       <c r="B212">
-        <v>0.658638</v>
+        <v>3.377631</v>
       </c>
       <c r="C212">
-        <v>-8.092851</v>
+        <v>-7.417046</v>
       </c>
       <c r="D212">
-        <v>0.968745</v>
+        <v>0.973028</v>
       </c>
     </row>
     <row r="213">
@@ -10772,13 +10772,13 @@
         </is>
       </c>
       <c r="B213">
-        <v>2.284252</v>
+        <v>4.811236</v>
       </c>
       <c r="C213">
-        <v>-7.810223</v>
+        <v>-6.600176</v>
       </c>
       <c r="D213">
-        <v>0.968738</v>
+        <v>0.973021</v>
       </c>
     </row>
     <row r="214">
@@ -10788,13 +10788,13 @@
         </is>
       </c>
       <c r="B214">
-        <v>3.819428</v>
+        <v>6.051397</v>
       </c>
       <c r="C214">
-        <v>-7.205463</v>
+        <v>-5.511828</v>
       </c>
       <c r="D214">
-        <v>0.968731</v>
+        <v>0.973013</v>
       </c>
     </row>
     <row r="215">
@@ -10804,13 +10804,13 @@
         </is>
       </c>
       <c r="B215">
-        <v>5.201441</v>
+        <v>7.048074</v>
       </c>
       <c r="C215">
-        <v>-6.304053</v>
+        <v>-4.196862</v>
       </c>
       <c r="D215">
-        <v>0.968723</v>
+        <v>0.973006</v>
       </c>
     </row>
     <row r="216">
@@ -10820,13 +10820,13 @@
         </is>
       </c>
       <c r="B216">
-        <v>6.374223</v>
+        <v>7.761411</v>
       </c>
       <c r="C216">
-        <v>-5.143414</v>
+        <v>-2.709028</v>
       </c>
       <c r="D216">
-        <v>0.968716</v>
+        <v>0.972999</v>
       </c>
     </row>
     <row r="217">
@@ -10836,13 +10836,13 @@
         </is>
       </c>
       <c r="B217">
-        <v>7.290567</v>
+        <v>8.163237</v>
       </c>
       <c r="C217">
-        <v>-3.771258</v>
+        <v>-1.108705</v>
       </c>
       <c r="D217">
-        <v>0.968709</v>
+        <v>0.972992</v>
       </c>
     </row>
     <row r="218">
@@ -10852,13 +10852,13 @@
         </is>
       </c>
       <c r="B218">
-        <v>7.913949</v>
+        <v>8.238072</v>
       </c>
       <c r="C218">
-        <v>-2.243549</v>
+        <v>0.539597</v>
       </c>
       <c r="D218">
-        <v>0.968702</v>
+        <v>0.972985</v>
       </c>
     </row>
     <row r="219">
@@ -10868,13 +10868,13 @@
         </is>
       </c>
       <c r="B219">
-        <v>8.219875</v>
+        <v>7.983611</v>
       </c>
       <c r="C219">
-        <v>-0.622157</v>
+        <v>2.169858</v>
       </c>
       <c r="D219">
-        <v>0.968695</v>
+        <v>0.972978</v>
       </c>
     </row>
     <row r="220">
@@ -10884,13 +10884,13 @@
         </is>
       </c>
       <c r="B220">
-        <v>8.196746</v>
+        <v>7.410677</v>
       </c>
       <c r="C220">
-        <v>1.027680</v>
+        <v>3.717193</v>
       </c>
       <c r="D220">
-        <v>0.968688</v>
+        <v>0.972971</v>
       </c>
     </row>
     <row r="221">
@@ -10900,13 +10900,13 @@
         </is>
       </c>
       <c r="B221">
-        <v>7.846175</v>
+        <v>6.542654</v>
       </c>
       <c r="C221">
-        <v>2.640008</v>
+        <v>5.120417</v>
       </c>
       <c r="D221">
-        <v>0.968681</v>
+        <v>0.972965</v>
       </c>
     </row>
     <row r="222">
@@ -10916,13 +10916,13 @@
         </is>
       </c>
       <c r="B222">
-        <v>7.182791</v>
+        <v>5.414432</v>
       </c>
       <c r="C222">
-        <v>4.150776</v>
+        <v>6.324416</v>
       </c>
       <c r="D222">
-        <v>0.968675</v>
+        <v>0.972958</v>
       </c>
     </row>
     <row r="223">
@@ -10932,13 +10932,13 @@
         </is>
       </c>
       <c r="B223">
-        <v>6.233519</v>
+        <v>4.070915</v>
       </c>
       <c r="C223">
-        <v>5.500363</v>
+        <v>7.282259</v>
       </c>
       <c r="D223">
-        <v>0.968668</v>
+        <v>0.972951</v>
       </c>
     </row>
     <row r="224">
@@ -10948,13 +10948,13 @@
         </is>
       </c>
       <c r="B224">
-        <v>5.036392</v>
+        <v>2.565159</v>
       </c>
       <c r="C224">
-        <v>6.635875</v>
+        <v>7.956942</v>
       </c>
       <c r="D224">
-        <v>0.968661</v>
+        <v>0.972945</v>
       </c>
     </row>
     <row r="225">
@@ -10964,13 +10964,13 @@
         </is>
       </c>
       <c r="B225">
-        <v>3.638939</v>
+        <v>0.956217</v>
       </c>
       <c r="C225">
-        <v>7.513157</v>
+        <v>8.322736</v>
       </c>
       <c r="D225">
-        <v>0.968655</v>
+        <v>0.972938</v>
       </c>
     </row>
   </sheetData>
